--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\serviciospostales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C0E117-F61B-405E-AADD-8F3DE2B682B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229452AA-060F-4217-8835-AA19DEC54C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E6FC639F-6B65-45D1-B277-37C7A7B6E063}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="21">
   <si>
     <t>daniel  hernandez</t>
   </si>
@@ -86,13 +86,31 @@
   </si>
   <si>
     <t>19 su</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>DIRECCION</t>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>COMUNA</t>
+  </si>
+  <si>
+    <t>DETALLE</t>
+  </si>
+  <si>
+    <t>TIPO ENCOMIENDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,13 +124,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -127,8 +159,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A875C10F-E6EF-4424-A512-1E629103B252}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -452,208 +486,230 @@
     <col min="6" max="6" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>